--- a/sample/種の在庫.xlsx
+++ b/sample/種の在庫.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t xml:space="preserve">番号</t>
   </si>
@@ -28,94 +28,172 @@
     <t xml:space="preserve">覚え書き</t>
   </si>
   <si>
+    <t xml:space="preserve">0001</t>
+  </si>
+  <si>
     <t xml:space="preserve">野菜</t>
   </si>
   <si>
     <t xml:space="preserve">青しそ</t>
   </si>
   <si>
+    <t xml:space="preserve">0002</t>
+  </si>
+  <si>
     <t xml:space="preserve">赤しそ</t>
   </si>
   <si>
+    <t xml:space="preserve">0003</t>
+  </si>
+  <si>
     <t xml:space="preserve">小松菜</t>
   </si>
   <si>
+    <t xml:space="preserve">0004</t>
+  </si>
+  <si>
     <t xml:space="preserve">水菜</t>
   </si>
   <si>
+    <t xml:space="preserve">0005</t>
+  </si>
+  <si>
     <t xml:space="preserve">春菊</t>
   </si>
   <si>
+    <t xml:space="preserve">0006</t>
+  </si>
+  <si>
     <t xml:space="preserve">二十日大根</t>
   </si>
   <si>
+    <t xml:space="preserve">0007</t>
+  </si>
+  <si>
     <t xml:space="preserve">聖護院かぶ</t>
   </si>
   <si>
+    <t xml:space="preserve">0008</t>
+  </si>
+  <si>
     <t xml:space="preserve">打木赤皮甘栗かぼちゃ</t>
   </si>
   <si>
+    <t xml:space="preserve">0009</t>
+  </si>
+  <si>
     <t xml:space="preserve">鹿ケ谷かぼちゃ</t>
   </si>
   <si>
+    <t xml:space="preserve">0010</t>
+  </si>
+  <si>
     <t xml:space="preserve">大和真菜</t>
   </si>
   <si>
+    <t xml:space="preserve">0011</t>
+  </si>
+  <si>
     <t xml:space="preserve">トマト</t>
   </si>
   <si>
     <t xml:space="preserve">ステラミニトマト</t>
   </si>
   <si>
+    <t xml:space="preserve">0012</t>
+  </si>
+  <si>
     <t xml:space="preserve">世界一トマト</t>
   </si>
   <si>
+    <t xml:space="preserve">0013</t>
+  </si>
+  <si>
     <t xml:space="preserve">ポンデローザ</t>
   </si>
   <si>
+    <t xml:space="preserve">0014</t>
+  </si>
+  <si>
     <t xml:space="preserve">黄金トマト</t>
   </si>
   <si>
+    <t xml:space="preserve">0015</t>
+  </si>
+  <si>
     <t xml:space="preserve">豆</t>
   </si>
   <si>
     <t xml:space="preserve">丹波黒大豆</t>
   </si>
   <si>
+    <t xml:space="preserve">0016</t>
+  </si>
+  <si>
     <t xml:space="preserve">鞍掛豆</t>
   </si>
   <si>
+    <t xml:space="preserve">0017</t>
+  </si>
+  <si>
     <t xml:space="preserve">花豆</t>
   </si>
   <si>
+    <t xml:space="preserve">0018</t>
+  </si>
+  <si>
     <t xml:space="preserve">青大豆</t>
   </si>
   <si>
+    <t xml:space="preserve">0019</t>
+  </si>
+  <si>
     <t xml:space="preserve">花</t>
   </si>
   <si>
     <t xml:space="preserve">松葉菊</t>
   </si>
   <si>
+    <t xml:space="preserve">0020</t>
+  </si>
+  <si>
     <t xml:space="preserve">千日紅</t>
   </si>
   <si>
+    <t xml:space="preserve">0021</t>
+  </si>
+  <si>
     <t xml:space="preserve">綿(和綿)</t>
   </si>
   <si>
+    <t xml:space="preserve">0022</t>
+  </si>
+  <si>
     <t xml:space="preserve">藍</t>
   </si>
   <si>
+    <t xml:space="preserve">0023</t>
+  </si>
+  <si>
     <t xml:space="preserve">薬草</t>
   </si>
   <si>
     <t xml:space="preserve">カモミール</t>
   </si>
   <si>
+    <t xml:space="preserve">0024</t>
+  </si>
+  <si>
     <t xml:space="preserve">エキナセア</t>
   </si>
   <si>
+    <t xml:space="preserve">0025</t>
+  </si>
+  <si>
     <t xml:space="preserve">レモンバーム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0026</t>
   </si>
   <si>
     <t xml:space="preserve">セントジョーンズワート</t>
@@ -196,14 +274,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2">
         <v>360</v>
@@ -213,14 +291,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2">
         <v>360</v>
@@ -230,14 +308,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2">
         <v>360</v>
@@ -247,14 +325,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>360</v>
@@ -264,14 +342,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2">
         <v>360</v>
@@ -281,14 +359,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="s">
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
         <v>360</v>
@@ -298,14 +376,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2">
         <v>420</v>
@@ -315,14 +393,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="s">
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
         <v>480</v>
@@ -332,28 +410,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="s">
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2">
         <v>480</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2">
         <v>420</v>
@@ -363,14 +441,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2">
         <v>480</v>
@@ -380,14 +458,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="s">
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2">
         <v>480</v>
@@ -397,14 +475,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="s">
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2">
         <v>520</v>
@@ -414,28 +492,28 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2">
         <v>520</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2">
         <v>400</v>
@@ -445,14 +523,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2">
         <v>400</v>
@@ -462,14 +540,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2">
         <v>440</v>
@@ -479,14 +557,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D19" s="2">
         <v>400</v>
@@ -496,14 +574,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="s">
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2">
         <v>300</v>
@@ -513,14 +591,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D21" s="2">
         <v>300</v>
@@ -530,14 +608,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2">
         <v>380</v>
@@ -547,14 +625,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2">
         <v>380</v>
@@ -564,14 +642,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2">
         <v>340</v>
@@ -581,14 +659,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="s">
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2">
         <v>420</v>
@@ -598,28 +676,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="s">
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D26" s="2">
         <v>340</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="s">
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D27" s="2">
         <v>420</v>

--- a/sample/種の在庫.xlsx
+++ b/sample/種の在庫.xlsx
@@ -243,6 +243,115 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
@@ -287,7 +396,7 @@
         <v>360</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -389,7 +498,7 @@
         <v>420</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
